--- a/Trabalho M2/OUTPUT_3.3.b_RN_ORIG_VS_NORM/Common/Resultados_RN_ORIG_vs_NORM.xlsx
+++ b/Trabalho M2/OUTPUT_3.3.b_RN_ORIG_VS_NORM/Common/Resultados_RN_ORIG_vs_NORM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="146" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="219" uniqueCount="51">
   <si>
     <t>rank_original</t>
   </si>
@@ -148,6 +148,24 @@
   </si>
   <si>
     <t>[5 5]</t>
+  </si>
+  <si>
+    <t>RN_MICE_NORM_Topo-14_trainlm_logsig_MF6_Div-0.6-0.2-0.2</t>
+  </si>
+  <si>
+    <t>RN_MICE_NORM_Topo-10_trainscg_softmax_MF6_Div-0.6-0.2-0.2</t>
+  </si>
+  <si>
+    <t>RN_MICE_ORIG_Topo-14_trainlm_logsig_MF6</t>
+  </si>
+  <si>
+    <t>RN_MICE_NORM_Topo-14_trainlm_logsig_MF6</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>[0.6 0.2 0.2]</t>
   </si>
 </sst>
 </file>
@@ -197,8 +215,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="true"/>
-    <col min="2" max="2" width="58.1796875" customWidth="true"/>
-    <col min="3" max="3" width="43" customWidth="true"/>
+    <col min="2" max="2" width="58" customWidth="true"/>
+    <col min="3" max="3" width="42.81640625" customWidth="true"/>
     <col min="4" max="4" width="8.7265625" customWidth="true"/>
     <col min="5" max="5" width="9.26953125" customWidth="true"/>
     <col min="6" max="6" width="8.1796875" customWidth="true"/>
@@ -214,7 +232,7 @@
     <col min="16" max="16" width="11.453125" customWidth="true"/>
     <col min="17" max="17" width="15.453125" customWidth="true"/>
     <col min="18" max="18" width="14.36328125" customWidth="true"/>
-    <col min="19" max="19" width="12.453125" customWidth="true"/>
+    <col min="19" max="19" width="10.81640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -281,10 +299,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>13</v>
@@ -293,7 +311,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>20</v>
@@ -305,34 +323,34 @@
         <v>25</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K2" s="0">
         <v>6</v>
       </c>
       <c r="L2" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M2" s="0">
-        <v>16.67695568945345</v>
+        <v>16.675286853517228</v>
       </c>
       <c r="N2" s="0">
-        <v>16.703021937374768</v>
+        <v>16.688128149311144</v>
       </c>
       <c r="O2" s="0">
-        <v>99.953333333333333</v>
+        <v>99.961999999999989</v>
       </c>
       <c r="P2" s="0">
-        <v>99.866666666666674</v>
+        <v>99.919999999999987</v>
       </c>
       <c r="Q2" s="0">
-        <v>20.333333333333332</v>
+        <v>23.600000000000001</v>
       </c>
       <c r="R2" s="0">
-        <v>15.666666666666666</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="S2" s="0">
-        <v>0.44966666666666671</v>
+        <v>0.7654000000000003</v>
       </c>
     </row>
     <row r="3">
@@ -340,10 +358,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>13</v>
@@ -352,7 +370,7 @@
         <v>16</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>20</v>
@@ -364,34 +382,34 @@
         <v>25</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K3" s="0">
         <v>6</v>
       </c>
       <c r="L3" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M3" s="0">
-        <v>17.607181651769086</v>
+        <v>16.674364445478624</v>
       </c>
       <c r="N3" s="0">
-        <v>17.671453080264726</v>
+        <v>16.685262211192239</v>
       </c>
       <c r="O3" s="0">
-        <v>88.759999999999991</v>
+        <v>99.976000000000013</v>
       </c>
       <c r="P3" s="0">
-        <v>88.177777777777763</v>
+        <v>99.950000000000003</v>
       </c>
       <c r="Q3" s="0">
-        <v>25</v>
+        <v>21.300000000000001</v>
       </c>
       <c r="R3" s="0">
-        <v>23.666666666666668</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="S3" s="0">
-        <v>0.5336666666666664</v>
+        <v>0.68410000000000015</v>
       </c>
     </row>
     <row r="4">
@@ -399,10 +417,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>13</v>
@@ -411,10 +429,10 @@
         <v>15</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>23</v>
@@ -429,28 +447,28 @@
         <v>6</v>
       </c>
       <c r="L4" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M4" s="0">
-        <v>16.702428881609944</v>
+        <v>17.156756324521929</v>
       </c>
       <c r="N4" s="0">
-        <v>16.73252662156742</v>
+        <v>17.179619358909047</v>
       </c>
       <c r="O4" s="0">
-        <v>99.906666666666652</v>
+        <v>98.334000000000003</v>
       </c>
       <c r="P4" s="0">
-        <v>99.822222222222237</v>
+        <v>98.26666666666668</v>
       </c>
       <c r="Q4" s="0">
-        <v>16.333333333333332</v>
+        <v>33</v>
       </c>
       <c r="R4" s="0">
-        <v>10.333333333333334</v>
+        <v>30.399999999999999</v>
       </c>
       <c r="S4" s="0">
-        <v>0.42600000000000016</v>
+        <v>0.31460000000000077</v>
       </c>
     </row>
     <row r="5">
@@ -458,10 +476,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>13</v>
@@ -470,10 +488,10 @@
         <v>16</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>23</v>
@@ -488,28 +506,28 @@
         <v>6</v>
       </c>
       <c r="L5" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M5" s="0">
-        <v>16.688487820048451</v>
+        <v>16.688622052188443</v>
       </c>
       <c r="N5" s="0">
-        <v>16.680003060215942</v>
+        <v>16.695001075291962</v>
       </c>
       <c r="O5" s="0">
-        <v>99.953333333333333</v>
+        <v>99.952000000000012</v>
       </c>
       <c r="P5" s="0">
-        <v>100</v>
+        <v>99.933333333333337</v>
       </c>
       <c r="Q5" s="0">
-        <v>31.666666666666668</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="R5" s="0">
-        <v>25.666666666666668</v>
+        <v>28.899999999999999</v>
       </c>
       <c r="S5" s="0">
-        <v>0.80833333333333357</v>
+        <v>0.29520000000000002</v>
       </c>
     </row>
     <row r="6">
@@ -517,10 +535,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>13</v>
@@ -532,7 +550,7 @@
         <v>18</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="0" t="s">
         <v>23</v>
@@ -541,34 +559,34 @@
         <v>26</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K6" s="0">
         <v>6</v>
       </c>
       <c r="L6" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M6" s="0">
-        <v>16.67261877913063</v>
+        <v>16.676642730876896</v>
       </c>
       <c r="N6" s="0">
-        <v>16.680526489090315</v>
+        <v>16.688310015035317</v>
       </c>
       <c r="O6" s="0">
-        <v>100</v>
+        <v>99.980000000000004</v>
       </c>
       <c r="P6" s="0">
-        <v>100</v>
+        <v>99.950000000000003</v>
       </c>
       <c r="Q6" s="0">
-        <v>29</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="R6" s="0">
-        <v>23</v>
+        <v>29.899999999999999</v>
       </c>
       <c r="S6" s="0">
-        <v>0.63999999999999935</v>
+        <v>0.30130000000000018</v>
       </c>
     </row>
     <row r="7">
@@ -576,10 +594,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>13</v>
@@ -591,7 +609,7 @@
         <v>18</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="0" t="s">
         <v>23</v>
@@ -600,34 +618,34 @@
         <v>26</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K7" s="0">
         <v>6</v>
       </c>
       <c r="L7" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M7" s="0">
-        <v>16.679322254595494</v>
+        <v>19.599901792060671</v>
       </c>
       <c r="N7" s="0">
-        <v>16.712137407823104</v>
+        <v>19.514462171128063</v>
       </c>
       <c r="O7" s="0">
-        <v>99.946666666666673</v>
+        <v>89.962000000000003</v>
       </c>
       <c r="P7" s="0">
-        <v>99.822222222222237</v>
+        <v>90.27000000000001</v>
       </c>
       <c r="Q7" s="0">
-        <v>35.666666666666664</v>
+        <v>40</v>
       </c>
       <c r="R7" s="0">
-        <v>29.666666666666668</v>
+        <v>36.899999999999999</v>
       </c>
       <c r="S7" s="0">
-        <v>0.78099999999999881</v>
+        <v>0.39329999999999987</v>
       </c>
     </row>
   </sheetData>
